--- a/results/block2_results/area/Synthetic_2/dataset_Synthetic_Synthetic_2.xlsx
+++ b/results/block2_results/area/Synthetic_2/dataset_Synthetic_Synthetic_2.xlsx
@@ -531,7 +531,7 @@
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4956798713022</v>
       </c>
     </row>
     <row r="3">
@@ -575,7 +575,7 @@
         <v>1</v>
       </c>
       <c r="L3" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4956864249835</v>
       </c>
     </row>
     <row r="4">
@@ -619,7 +619,7 @@
         <v>2</v>
       </c>
       <c r="L4" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4972710745226</v>
       </c>
     </row>
     <row r="5">
@@ -663,7 +663,7 @@
         <v>3</v>
       </c>
       <c r="L5" t="n">
-        <v>314.1592653589793</v>
+        <v>333.624825899545</v>
       </c>
     </row>
     <row r="6">
@@ -707,7 +707,7 @@
         <v>4</v>
       </c>
       <c r="L6" t="n">
-        <v>314.1592653589793</v>
+        <v>316.5201844920101</v>
       </c>
     </row>
     <row r="7">
@@ -751,7 +751,7 @@
         <v>5</v>
       </c>
       <c r="L7" t="n">
-        <v>314.1592653589793</v>
+        <v>316.5201759106017</v>
       </c>
     </row>
     <row r="8">
@@ -795,7 +795,7 @@
         <v>6</v>
       </c>
       <c r="L8" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4933721855287</v>
       </c>
     </row>
     <row r="9">
@@ -839,7 +839,7 @@
         <v>7</v>
       </c>
       <c r="L9" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4938953908455</v>
       </c>
     </row>
     <row r="10">
@@ -883,7 +883,7 @@
         <v>8</v>
       </c>
       <c r="L10" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4942734305535</v>
       </c>
     </row>
     <row r="11">
@@ -927,7 +927,7 @@
         <v>9</v>
       </c>
       <c r="L11" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4938489206801</v>
       </c>
     </row>
     <row r="12">
@@ -971,7 +971,7 @@
         <v>10</v>
       </c>
       <c r="L12" t="n">
-        <v>314.1592653589793</v>
+        <v>316.5117826027279</v>
       </c>
     </row>
     <row r="13">
@@ -1015,7 +1015,7 @@
         <v>11</v>
       </c>
       <c r="L13" t="n">
-        <v>314.1592653589793</v>
+        <v>316.5118241388803</v>
       </c>
     </row>
     <row r="14">
@@ -1059,7 +1059,7 @@
         <v>12</v>
       </c>
       <c r="L14" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4951254556041</v>
       </c>
     </row>
     <row r="15">
@@ -1103,7 +1103,7 @@
         <v>13</v>
       </c>
       <c r="L15" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4960806526422</v>
       </c>
     </row>
     <row r="16">
@@ -1147,7 +1147,7 @@
         <v>14</v>
       </c>
       <c r="L16" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4996263630704</v>
       </c>
     </row>
     <row r="17">
@@ -1191,7 +1191,7 @@
         <v>15</v>
       </c>
       <c r="L17" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4977227416219</v>
       </c>
     </row>
     <row r="18">
@@ -1235,7 +1235,7 @@
         <v>16</v>
       </c>
       <c r="L18" t="n">
-        <v>314.1592653589793</v>
+        <v>319.119833396043</v>
       </c>
     </row>
     <row r="19">
@@ -1279,7 +1279,7 @@
         <v>17</v>
       </c>
       <c r="L19" t="n">
-        <v>314.1592653589793</v>
+        <v>316.8977388744225</v>
       </c>
     </row>
     <row r="20">
@@ -1323,7 +1323,7 @@
         <v>18</v>
       </c>
       <c r="L20" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4982004585777</v>
       </c>
     </row>
     <row r="21">
@@ -1367,7 +1367,7 @@
         <v>19</v>
       </c>
       <c r="L21" t="n">
-        <v>314.1592653589793</v>
+        <v>316.5041631445446</v>
       </c>
     </row>
     <row r="22">
@@ -1411,7 +1411,7 @@
         <v>20</v>
       </c>
       <c r="L22" t="n">
-        <v>314.1592653589793</v>
+        <v>316.8191053532236</v>
       </c>
     </row>
     <row r="23">
@@ -1455,7 +1455,7 @@
         <v>21</v>
       </c>
       <c r="L23" t="n">
-        <v>314.1592653589793</v>
+        <v>316.8192663418636</v>
       </c>
     </row>
     <row r="24">
@@ -1499,7 +1499,7 @@
         <v>22</v>
       </c>
       <c r="L24" t="n">
-        <v>314.1592653589793</v>
+        <v>316.5335092876441</v>
       </c>
     </row>
     <row r="25">
@@ -1543,7 +1543,7 @@
         <v>23</v>
       </c>
       <c r="L25" t="n">
-        <v>314.1592653589793</v>
+        <v>316.5384922424669</v>
       </c>
     </row>
     <row r="26">
@@ -1587,7 +1587,7 @@
         <v>24</v>
       </c>
       <c r="L26" t="n">
-        <v>314.1592653589793</v>
+        <v>316.560670066318</v>
       </c>
     </row>
     <row r="27">
@@ -1631,7 +1631,7 @@
         <v>25</v>
       </c>
       <c r="L27" t="n">
-        <v>314.1592653589793</v>
+        <v>316.8514915084962</v>
       </c>
     </row>
     <row r="28">
@@ -1675,7 +1675,7 @@
         <v>26</v>
       </c>
       <c r="L28" t="n">
-        <v>314.1592653589793</v>
+        <v>316.5930693749811</v>
       </c>
     </row>
     <row r="29">
@@ -1719,7 +1719,7 @@
         <v>27</v>
       </c>
       <c r="L29" t="n">
-        <v>314.1592653589793</v>
+        <v>316.6223582354581</v>
       </c>
     </row>
     <row r="30">
@@ -1763,7 +1763,7 @@
         <v>28</v>
       </c>
       <c r="L30" t="n">
-        <v>314.1592653589793</v>
+        <v>316.6357038559812</v>
       </c>
     </row>
     <row r="31">
@@ -1807,7 +1807,7 @@
         <v>29</v>
       </c>
       <c r="L31" t="n">
-        <v>314.1592653589793</v>
+        <v>316.6418857289111</v>
       </c>
     </row>
     <row r="32">
@@ -1851,7 +1851,7 @@
         <v>30</v>
       </c>
       <c r="L32" t="n">
-        <v>314.1592653589793</v>
+        <v>316.6143668288898</v>
       </c>
     </row>
     <row r="33">
@@ -1895,7 +1895,7 @@
         <v>31</v>
       </c>
       <c r="L33" t="n">
-        <v>314.1592653589793</v>
+        <v>316.5626661416117</v>
       </c>
     </row>
     <row r="34">
@@ -1939,7 +1939,7 @@
         <v>32</v>
       </c>
       <c r="L34" t="n">
-        <v>314.1592653589793</v>
+        <v>316.5778275061289</v>
       </c>
     </row>
     <row r="35">
@@ -1983,7 +1983,7 @@
         <v>33</v>
       </c>
       <c r="L35" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4519340162132</v>
       </c>
     </row>
     <row r="36">
@@ -2027,7 +2027,7 @@
         <v>34</v>
       </c>
       <c r="L36" t="n">
-        <v>314.1592653589793</v>
+        <v>316.3463324831218</v>
       </c>
     </row>
     <row r="37">
@@ -2071,7 +2071,7 @@
         <v>35</v>
       </c>
       <c r="L37" t="n">
-        <v>314.1592653589793</v>
+        <v>316.346243104606</v>
       </c>
     </row>
     <row r="38">
@@ -2115,7 +2115,7 @@
         <v>36</v>
       </c>
       <c r="L38" t="n">
-        <v>314.1592653589793</v>
+        <v>316.336112816567</v>
       </c>
     </row>
     <row r="39">
@@ -2159,7 +2159,7 @@
         <v>37</v>
       </c>
       <c r="L39" t="n">
-        <v>314.1592653589793</v>
+        <v>316.2260680509127</v>
       </c>
     </row>
     <row r="40">
@@ -2203,7 +2203,7 @@
         <v>38</v>
       </c>
       <c r="L40" t="n">
-        <v>314.1592653589793</v>
+        <v>316.248869489448</v>
       </c>
     </row>
     <row r="41">
@@ -2247,7 +2247,7 @@
         <v>39</v>
       </c>
       <c r="L41" t="n">
-        <v>314.1592653589793</v>
+        <v>316.240549678392</v>
       </c>
     </row>
     <row r="42">
@@ -2291,7 +2291,7 @@
         <v>40</v>
       </c>
       <c r="L42" t="n">
-        <v>314.1592653589793</v>
+        <v>318.0867669719897</v>
       </c>
     </row>
     <row r="43">
@@ -2335,7 +2335,7 @@
         <v>41</v>
       </c>
       <c r="L43" t="n">
-        <v>314.1592653589793</v>
+        <v>316.3770358521283</v>
       </c>
     </row>
     <row r="44">
@@ -2379,7 +2379,7 @@
         <v>42</v>
       </c>
       <c r="L44" t="n">
-        <v>314.1592653589793</v>
+        <v>317.3452100740342</v>
       </c>
     </row>
     <row r="45">
@@ -2423,7 +2423,7 @@
         <v>43</v>
       </c>
       <c r="L45" t="n">
-        <v>314.1592653589793</v>
+        <v>322.7839979743623</v>
       </c>
     </row>
     <row r="46">
@@ -2467,7 +2467,7 @@
         <v>44</v>
       </c>
       <c r="L46" t="n">
-        <v>314.1592653589793</v>
+        <v>322.7839805802706</v>
       </c>
     </row>
     <row r="47">
@@ -2511,7 +2511,7 @@
         <v>45</v>
       </c>
       <c r="L47" t="n">
-        <v>314.1592653589793</v>
+        <v>317.765308243337</v>
       </c>
     </row>
     <row r="48">
@@ -2555,7 +2555,7 @@
         <v>46</v>
       </c>
       <c r="L48" t="n">
-        <v>314.1592653589793</v>
+        <v>318.0898230931229</v>
       </c>
     </row>
     <row r="49">
@@ -2599,7 +2599,7 @@
         <v>47</v>
       </c>
       <c r="L49" t="n">
-        <v>314.1592653589793</v>
+        <v>318.0311875471213</v>
       </c>
     </row>
     <row r="50">
@@ -2643,7 +2643,7 @@
         <v>48</v>
       </c>
       <c r="L50" t="n">
-        <v>314.1592653589793</v>
+        <v>318.6565806888216</v>
       </c>
     </row>
     <row r="51">
@@ -2687,7 +2687,7 @@
         <v>49</v>
       </c>
       <c r="L51" t="n">
-        <v>314.1592653589793</v>
+        <v>317.2623272318006</v>
       </c>
     </row>
     <row r="52">
@@ -2731,7 +2731,7 @@
         <v>50</v>
       </c>
       <c r="L52" t="n">
-        <v>314.1592653589793</v>
+        <v>316.5411432908892</v>
       </c>
     </row>
     <row r="53">
@@ -2775,7 +2775,7 @@
         <v>51</v>
       </c>
       <c r="L53" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4174930269139</v>
       </c>
     </row>
     <row r="54">
@@ -2819,7 +2819,7 @@
         <v>52</v>
       </c>
       <c r="L54" t="n">
-        <v>314.1592653589793</v>
+        <v>315.186469065413</v>
       </c>
     </row>
     <row r="55">
@@ -2863,7 +2863,7 @@
         <v>53</v>
       </c>
       <c r="L55" t="n">
-        <v>314.1592653589793</v>
+        <v>315.3488601235974</v>
       </c>
     </row>
     <row r="56">
@@ -2907,7 +2907,7 @@
         <v>54</v>
       </c>
       <c r="L56" t="n">
-        <v>314.1592653589793</v>
+        <v>314.8568266646905</v>
       </c>
     </row>
     <row r="57">
@@ -2951,7 +2951,7 @@
         <v>55</v>
       </c>
       <c r="L57" t="n">
-        <v>314.1315652890347</v>
+        <v>313.3667832967068</v>
       </c>
     </row>
     <row r="58">
@@ -2995,7 +2995,7 @@
         <v>56</v>
       </c>
       <c r="L58" t="n">
-        <v>313.8378490533948</v>
+        <v>312.0935691643398</v>
       </c>
     </row>
     <row r="59">
@@ -3039,7 +3039,7 @@
         <v>57</v>
       </c>
       <c r="L59" t="n">
-        <v>313.6108872403111</v>
+        <v>311.512646269697</v>
       </c>
     </row>
     <row r="60">
@@ -3083,7 +3083,7 @@
         <v>58</v>
       </c>
       <c r="L60" t="n">
-        <v>313.609850167252</v>
+        <v>311.8112845122635</v>
       </c>
     </row>
     <row r="61">
@@ -3127,7 +3127,7 @@
         <v>59</v>
       </c>
       <c r="L61" t="n">
-        <v>311.7276708407379</v>
+        <v>308.657563515286</v>
       </c>
     </row>
     <row r="62">
@@ -3171,7 +3171,7 @@
         <v>60</v>
       </c>
       <c r="L62" t="n">
-        <v>311.1252778901723</v>
+        <v>308.0233956472299</v>
       </c>
     </row>
     <row r="63">
@@ -3215,7 +3215,7 @@
         <v>61</v>
       </c>
       <c r="L63" t="n">
-        <v>307.8119344940786</v>
+        <v>304.4916221213158</v>
       </c>
     </row>
     <row r="64">
@@ -3259,7 +3259,7 @@
         <v>62</v>
       </c>
       <c r="L64" t="n">
-        <v>303.9601468164716</v>
+        <v>300.5870753959373</v>
       </c>
     </row>
     <row r="65">
@@ -3303,7 +3303,7 @@
         <v>63</v>
       </c>
       <c r="L65" t="n">
-        <v>299.4512167284911</v>
+        <v>296.8007748403156</v>
       </c>
     </row>
     <row r="66">
@@ -3347,7 +3347,7 @@
         <v>64</v>
       </c>
       <c r="L66" t="n">
-        <v>294.6269652508399</v>
+        <v>292.6089091826404</v>
       </c>
     </row>
     <row r="67">
@@ -3391,7 +3391,7 @@
         <v>65</v>
       </c>
       <c r="L67" t="n">
-        <v>289.6914968457265</v>
+        <v>288.0497510411172</v>
       </c>
     </row>
     <row r="68">
@@ -3435,7 +3435,7 @@
         <v>66</v>
       </c>
       <c r="L68" t="n">
-        <v>286.2196126656559</v>
+        <v>285.0381023203544</v>
       </c>
     </row>
     <row r="69">
@@ -3479,7 +3479,7 @@
         <v>67</v>
       </c>
       <c r="L69" t="n">
-        <v>253.4092476203645</v>
+        <v>254.9553963130502</v>
       </c>
     </row>
     <row r="70">
@@ -3523,7 +3523,7 @@
         <v>68</v>
       </c>
       <c r="L70" t="n">
-        <v>251.0332160772647</v>
+        <v>252.5607021558965</v>
       </c>
     </row>
     <row r="71">
@@ -3567,7 +3567,7 @@
         <v>69</v>
       </c>
       <c r="L71" t="n">
-        <v>251.0139509799078</v>
+        <v>252.5458388685716</v>
       </c>
     </row>
     <row r="72">
@@ -3611,7 +3611,7 @@
         <v>70</v>
       </c>
       <c r="L72" t="n">
-        <v>234.6376077615358</v>
+        <v>236.6410918994229</v>
       </c>
     </row>
     <row r="73">
@@ -3655,7 +3655,7 @@
         <v>71</v>
       </c>
       <c r="L73" t="n">
-        <v>231.3715413458951</v>
+        <v>233.4640201931528</v>
       </c>
     </row>
     <row r="74">
@@ -3699,7 +3699,7 @@
         <v>72</v>
       </c>
       <c r="L74" t="n">
-        <v>230.1589532726078</v>
+        <v>233.5399884210641</v>
       </c>
     </row>
     <row r="75">
@@ -3743,7 +3743,7 @@
         <v>73</v>
       </c>
       <c r="L75" t="n">
-        <v>226.2688907452621</v>
+        <v>229.0752350057351</v>
       </c>
     </row>
     <row r="76">
@@ -3787,7 +3787,7 @@
         <v>74</v>
       </c>
       <c r="L76" t="n">
-        <v>225.0301843118329</v>
+        <v>227.8577603933362</v>
       </c>
     </row>
     <row r="77">
@@ -3831,7 +3831,7 @@
         <v>75</v>
       </c>
       <c r="L77" t="n">
-        <v>225.0251857356426</v>
+        <v>227.8527994053118</v>
       </c>
     </row>
     <row r="78">
@@ -3875,7 +3875,7 @@
         <v>76</v>
       </c>
       <c r="L78" t="n">
-        <v>213.719050856379</v>
+        <v>215.8886209778705</v>
       </c>
     </row>
     <row r="79">
@@ -3919,7 +3919,7 @@
         <v>77</v>
       </c>
       <c r="L79" t="n">
-        <v>201.9262946834099</v>
+        <v>204.0270110073141</v>
       </c>
     </row>
     <row r="80">
@@ -3963,7 +3963,7 @@
         <v>78</v>
       </c>
       <c r="L80" t="n">
-        <v>200.1233890670008</v>
+        <v>203.3757378729639</v>
       </c>
     </row>
     <row r="81">
@@ -4007,7 +4007,7 @@
         <v>79</v>
       </c>
       <c r="L81" t="n">
-        <v>198.4697210122667</v>
+        <v>202.162792105526</v>
       </c>
     </row>
     <row r="82">
@@ -4051,7 +4051,7 @@
         <v>80</v>
       </c>
       <c r="L82" t="n">
-        <v>197.5281152127406</v>
+        <v>199.560790903416</v>
       </c>
     </row>
     <row r="83">
@@ -4095,7 +4095,7 @@
         <v>81</v>
       </c>
       <c r="L83" t="n">
-        <v>197.5050285414572</v>
+        <v>199.53895674502</v>
       </c>
     </row>
     <row r="84">
@@ -4139,7 +4139,7 @@
         <v>82</v>
       </c>
       <c r="L84" t="n">
-        <v>194.6181629775267</v>
+        <v>198.0488042536388</v>
       </c>
     </row>
     <row r="85">
@@ -4183,7 +4183,7 @@
         <v>83</v>
       </c>
       <c r="L85" t="n">
-        <v>191.4538906498383</v>
+        <v>194.3516413732588</v>
       </c>
     </row>
     <row r="86">
@@ -4227,7 +4227,7 @@
         <v>84</v>
       </c>
       <c r="L86" t="n">
-        <v>180.5367905217445</v>
+        <v>183.2890629174703</v>
       </c>
     </row>
     <row r="87">
@@ -4271,7 +4271,7 @@
         <v>85</v>
       </c>
       <c r="L87" t="n">
-        <v>179.3146318707147</v>
+        <v>181.1452928466024</v>
       </c>
     </row>
     <row r="88">
@@ -4315,7 +4315,7 @@
         <v>86</v>
       </c>
       <c r="L88" t="n">
-        <v>175.6268913642302</v>
+        <v>178.7889751279239</v>
       </c>
     </row>
     <row r="89">
@@ -4359,7 +4359,7 @@
         <v>87</v>
       </c>
       <c r="L89" t="n">
-        <v>167.6902340874137</v>
+        <v>170.0510698939867</v>
       </c>
     </row>
     <row r="90">
@@ -4403,7 +4403,7 @@
         <v>88</v>
       </c>
       <c r="L90" t="n">
-        <v>156.2610422305858</v>
+        <v>158.173188195218</v>
       </c>
     </row>
     <row r="91">
@@ -4447,7 +4447,7 @@
         <v>89</v>
       </c>
       <c r="L91" t="n">
-        <v>150.422316992052</v>
+        <v>152.1045352101532</v>
       </c>
     </row>
     <row r="92">
@@ -4491,7 +4491,7 @@
         <v>90</v>
       </c>
       <c r="L92" t="n">
-        <v>143.991974532357</v>
+        <v>144.8424016943108</v>
       </c>
     </row>
     <row r="93">
@@ -4535,7 +4535,7 @@
         <v>91</v>
       </c>
       <c r="L93" t="n">
-        <v>142.4192832986008</v>
+        <v>144.7702614025382</v>
       </c>
     </row>
     <row r="94">
@@ -4579,7 +4579,7 @@
         <v>92</v>
       </c>
       <c r="L94" t="n">
-        <v>133.5845032849845</v>
+        <v>136.4629930245137</v>
       </c>
     </row>
     <row r="95">
@@ -4623,7 +4623,7 @@
         <v>93</v>
       </c>
       <c r="L95" t="n">
-        <v>127.7892139266595</v>
+        <v>128.6927136711962</v>
       </c>
     </row>
     <row r="96">
@@ -4667,7 +4667,7 @@
         <v>94</v>
       </c>
       <c r="L96" t="n">
-        <v>122.9627839138132</v>
+        <v>123.891393669422</v>
       </c>
     </row>
     <row r="97">
@@ -4711,7 +4711,7 @@
         <v>95</v>
       </c>
       <c r="L97" t="n">
-        <v>120.4741900327024</v>
+        <v>121.9876728255553</v>
       </c>
     </row>
     <row r="98">
@@ -4755,7 +4755,7 @@
         <v>96</v>
       </c>
       <c r="L98" t="n">
-        <v>115.6536624166284</v>
+        <v>118.3273414111442</v>
       </c>
     </row>
     <row r="99">
@@ -4799,7 +4799,7 @@
         <v>97</v>
       </c>
       <c r="L99" t="n">
-        <v>113.7748396201627</v>
+        <v>117.1992547452434</v>
       </c>
     </row>
     <row r="100">
@@ -4843,7 +4843,7 @@
         <v>98</v>
       </c>
       <c r="L100" t="n">
-        <v>113.243490844349</v>
+        <v>115.2550096237926</v>
       </c>
     </row>
     <row r="101">
@@ -4887,7 +4887,7 @@
         <v>99</v>
       </c>
       <c r="L101" t="n">
-        <v>106.2771300804204</v>
+        <v>108.5548647407316</v>
       </c>
     </row>
     <row r="102">
@@ -4931,7 +4931,7 @@
         <v>100</v>
       </c>
       <c r="L102" t="n">
-        <v>102.5023719492844</v>
+        <v>105.5763520686886</v>
       </c>
     </row>
     <row r="103">
@@ -4975,7 +4975,7 @@
         <v>101</v>
       </c>
       <c r="L103" t="n">
-        <v>93.64567667079508</v>
+        <v>96.35646782615883</v>
       </c>
     </row>
     <row r="104">
@@ -5019,7 +5019,7 @@
         <v>102</v>
       </c>
       <c r="L104" t="n">
-        <v>90.05582729134076</v>
+        <v>93.25224740780769</v>
       </c>
     </row>
     <row r="105">
@@ -5063,7 +5063,7 @@
         <v>103</v>
       </c>
       <c r="L105" t="n">
-        <v>89.49439391321327</v>
+        <v>92.85329899001819</v>
       </c>
     </row>
     <row r="106">
@@ -5107,7 +5107,7 @@
         <v>104</v>
       </c>
       <c r="L106" t="n">
-        <v>89.48990858379221</v>
+        <v>92.85765641186558</v>
       </c>
     </row>
     <row r="107">
@@ -5151,7 +5151,7 @@
         <v>105</v>
       </c>
       <c r="L107" t="n">
-        <v>89.22175764386837</v>
+        <v>92.55685964381007</v>
       </c>
     </row>
     <row r="108">
@@ -5195,7 +5195,7 @@
         <v>106</v>
       </c>
       <c r="L108" t="n">
-        <v>89.22066299370901</v>
+        <v>92.49349973125699</v>
       </c>
     </row>
     <row r="109">
@@ -5239,7 +5239,7 @@
         <v>107</v>
       </c>
       <c r="L109" t="n">
-        <v>86.40674033045698</v>
+        <v>90.17524071230476</v>
       </c>
     </row>
     <row r="110">
@@ -5283,7 +5283,7 @@
         <v>108</v>
       </c>
       <c r="L110" t="n">
-        <v>82.71263007328757</v>
+        <v>86.76001954747389</v>
       </c>
     </row>
     <row r="111">
@@ -5327,7 +5327,7 @@
         <v>109</v>
       </c>
       <c r="L111" t="n">
-        <v>81.8895033996283</v>
+        <v>85.85532572715697</v>
       </c>
     </row>
     <row r="112">
@@ -5371,7 +5371,7 @@
         <v>110</v>
       </c>
       <c r="L112" t="n">
-        <v>81.88574721673176</v>
+        <v>85.86371882954251</v>
       </c>
     </row>
     <row r="113">
@@ -5415,7 +5415,7 @@
         <v>111</v>
       </c>
       <c r="L113" t="n">
-        <v>80.89730684178663</v>
+        <v>84.83428522776696</v>
       </c>
     </row>
     <row r="114">
@@ -5459,7 +5459,7 @@
         <v>112</v>
       </c>
       <c r="L114" t="n">
-        <v>80.890045133328</v>
+        <v>84.82789715314635</v>
       </c>
     </row>
     <row r="115">
@@ -5503,7 +5503,7 @@
         <v>113</v>
       </c>
       <c r="L115" t="n">
-        <v>78.5399454490972</v>
+        <v>82.64878673439914</v>
       </c>
     </row>
     <row r="116">
@@ -5547,7 +5547,7 @@
         <v>114</v>
       </c>
       <c r="L116" t="n">
-        <v>78.57412092513516</v>
+        <v>82.5503367289798</v>
       </c>
     </row>
     <row r="117">
@@ -5591,7 +5591,7 @@
         <v>115</v>
       </c>
       <c r="L117" t="n">
-        <v>78.57949973743237</v>
+        <v>83.23419294311364</v>
       </c>
     </row>
     <row r="118">
@@ -5635,7 +5635,7 @@
         <v>116</v>
       </c>
       <c r="L118" t="n">
-        <v>78.69586983587868</v>
+        <v>83.24048247981317</v>
       </c>
     </row>
     <row r="119">
@@ -5679,7 +5679,7 @@
         <v>117</v>
       </c>
       <c r="L119" t="n">
-        <v>82.09356063317179</v>
+        <v>86.28379979319364</v>
       </c>
     </row>
     <row r="120">
@@ -5723,7 +5723,7 @@
         <v>118</v>
       </c>
       <c r="L120" t="n">
-        <v>82.63013147238911</v>
+        <v>87.79940414161152</v>
       </c>
     </row>
     <row r="121">
@@ -5767,7 +5767,7 @@
         <v>119</v>
       </c>
       <c r="L121" t="n">
-        <v>105.5564219307495</v>
+        <v>107.33629442719</v>
       </c>
     </row>
     <row r="122">
@@ -5811,7 +5811,7 @@
         <v>120</v>
       </c>
       <c r="L122" t="n">
-        <v>109.3492294622752</v>
+        <v>113.8706623951545</v>
       </c>
     </row>
     <row r="123">
@@ -5855,7 +5855,7 @@
         <v>121</v>
       </c>
       <c r="L123" t="n">
-        <v>110.149534732799</v>
+        <v>114.6667286416566</v>
       </c>
     </row>
     <row r="124">
@@ -5899,7 +5899,7 @@
         <v>122</v>
       </c>
       <c r="L124" t="n">
-        <v>135.9921309828678</v>
+        <v>162.3056812330665</v>
       </c>
     </row>
     <row r="125">
@@ -5943,7 +5943,7 @@
         <v>123</v>
       </c>
       <c r="L125" t="n">
-        <v>136.4631495273463</v>
+        <v>162.8648876385568</v>
       </c>
     </row>
     <row r="126">
@@ -5987,7 +5987,7 @@
         <v>124</v>
       </c>
       <c r="L126" t="n">
-        <v>175.9755522072987</v>
+        <v>177.7578780679024</v>
       </c>
     </row>
     <row r="127">
@@ -6031,7 +6031,7 @@
         <v>125</v>
       </c>
       <c r="L127" t="n">
-        <v>191.753677956091</v>
+        <v>197.8936699667733</v>
       </c>
     </row>
     <row r="128">
@@ -6075,7 +6075,7 @@
         <v>126</v>
       </c>
       <c r="L128" t="n">
-        <v>195.3400059676167</v>
+        <v>201.5387278176926</v>
       </c>
     </row>
     <row r="129">
@@ -6119,7 +6119,7 @@
         <v>127</v>
       </c>
       <c r="L129" t="n">
-        <v>231.9376528434134</v>
+        <v>234.0298894599115</v>
       </c>
     </row>
     <row r="130">
@@ -6163,7 +6163,7 @@
         <v>128</v>
       </c>
       <c r="L130" t="n">
-        <v>234.9184160202003</v>
+        <v>237.416804129758</v>
       </c>
     </row>
     <row r="131">
@@ -6207,7 +6207,7 @@
         <v>129</v>
       </c>
       <c r="L131" t="n">
-        <v>294.9855223413448</v>
+        <v>291.1335317844975</v>
       </c>
     </row>
     <row r="132">
@@ -6251,7 +6251,7 @@
         <v>130</v>
       </c>
       <c r="L132" t="n">
-        <v>295.365127176615</v>
+        <v>291.4729142988677</v>
       </c>
     </row>
     <row r="133">
@@ -6295,7 +6295,7 @@
         <v>131</v>
       </c>
       <c r="L133" t="n">
-        <v>314.1592653589793</v>
+        <v>313.738845030075</v>
       </c>
     </row>
     <row r="134">
@@ -6339,7 +6339,7 @@
         <v>132</v>
       </c>
       <c r="L134" t="n">
-        <v>314.1592653589793</v>
+        <v>315.6279461454779</v>
       </c>
     </row>
     <row r="135">
@@ -6383,7 +6383,7 @@
         <v>133</v>
       </c>
       <c r="L135" t="n">
-        <v>314.1592653589793</v>
+        <v>316.1547027829528</v>
       </c>
     </row>
     <row r="136">
@@ -6427,7 +6427,7 @@
         <v>134</v>
       </c>
       <c r="L136" t="n">
-        <v>314.1592653589793</v>
+        <v>317.8526104247872</v>
       </c>
     </row>
     <row r="137">
@@ -6471,7 +6471,7 @@
         <v>135</v>
       </c>
       <c r="L137" t="n">
-        <v>314.1592653589793</v>
+        <v>317.6236624786501</v>
       </c>
     </row>
     <row r="138">
@@ -6515,7 +6515,7 @@
         <v>136</v>
       </c>
       <c r="L138" t="n">
-        <v>314.1592653589793</v>
+        <v>317.5916436821873</v>
       </c>
     </row>
     <row r="139">
@@ -6559,7 +6559,7 @@
         <v>137</v>
       </c>
       <c r="L139" t="n">
-        <v>314.1592653589793</v>
+        <v>317.6134253926882</v>
       </c>
     </row>
     <row r="140">
@@ -6603,7 +6603,7 @@
         <v>138</v>
       </c>
       <c r="L140" t="n">
-        <v>314.1592653589793</v>
+        <v>317.6880296600202</v>
       </c>
     </row>
     <row r="141">
@@ -6647,7 +6647,7 @@
         <v>139</v>
       </c>
       <c r="L141" t="n">
-        <v>314.1592653589793</v>
+        <v>317.7533179952903</v>
       </c>
     </row>
     <row r="142">
@@ -6691,7 +6691,7 @@
         <v>140</v>
       </c>
       <c r="L142" t="n">
-        <v>314.1592653589793</v>
+        <v>317.3627434845538</v>
       </c>
     </row>
     <row r="143">
@@ -6735,7 +6735,7 @@
         <v>141</v>
       </c>
       <c r="L143" t="n">
-        <v>314.1592653589793</v>
+        <v>316.6539549424615</v>
       </c>
     </row>
     <row r="144">
@@ -6779,7 +6779,7 @@
         <v>142</v>
       </c>
       <c r="L144" t="n">
-        <v>314.1592653589793</v>
+        <v>316.435102604766</v>
       </c>
     </row>
     <row r="145">
@@ -6823,7 +6823,7 @@
         <v>143</v>
       </c>
       <c r="L145" t="n">
-        <v>314.1592653589793</v>
+        <v>316.3049316578601</v>
       </c>
     </row>
     <row r="146">
@@ -6867,7 +6867,7 @@
         <v>144</v>
       </c>
       <c r="L146" t="n">
-        <v>314.1592653589793</v>
+        <v>316.2687233454461</v>
       </c>
     </row>
     <row r="147">
@@ -6911,7 +6911,7 @@
         <v>145</v>
       </c>
       <c r="L147" t="n">
-        <v>314.1592653589793</v>
+        <v>316.2166706769734</v>
       </c>
     </row>
     <row r="148">
@@ -6955,7 +6955,7 @@
         <v>146</v>
       </c>
       <c r="L148" t="n">
-        <v>314.1592653589793</v>
+        <v>316.3449265579602</v>
       </c>
     </row>
     <row r="149">
@@ -6999,7 +6999,7 @@
         <v>147</v>
       </c>
       <c r="L149" t="n">
-        <v>314.1592653589793</v>
+        <v>316.3255547191517</v>
       </c>
     </row>
     <row r="150">
@@ -7043,7 +7043,7 @@
         <v>148</v>
       </c>
       <c r="L150" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4511346509275</v>
       </c>
     </row>
     <row r="151">
@@ -7087,7 +7087,7 @@
         <v>149</v>
       </c>
       <c r="L151" t="n">
-        <v>314.1592653589793</v>
+        <v>316.5479574518906</v>
       </c>
     </row>
     <row r="152">
@@ -7131,7 +7131,7 @@
         <v>150</v>
       </c>
       <c r="L152" t="n">
-        <v>314.1592653589793</v>
+        <v>316.7052154824808</v>
       </c>
     </row>
     <row r="153">
@@ -7175,7 +7175,7 @@
         <v>151</v>
       </c>
       <c r="L153" t="n">
-        <v>314.1592653589793</v>
+        <v>316.5485923506799</v>
       </c>
     </row>
     <row r="154">
@@ -7219,7 +7219,7 @@
         <v>152</v>
       </c>
       <c r="L154" t="n">
-        <v>314.1592653589793</v>
+        <v>316.6194114183377</v>
       </c>
     </row>
     <row r="155">
@@ -7263,7 +7263,7 @@
         <v>153</v>
       </c>
       <c r="L155" t="n">
-        <v>314.1592653589793</v>
+        <v>316.6371955020049</v>
       </c>
     </row>
     <row r="156">
@@ -7307,7 +7307,7 @@
         <v>154</v>
       </c>
       <c r="L156" t="n">
-        <v>314.1592653589793</v>
+        <v>316.6496597587351</v>
       </c>
     </row>
     <row r="157">
@@ -7351,7 +7351,7 @@
         <v>155</v>
       </c>
       <c r="L157" t="n">
-        <v>314.1592653589793</v>
+        <v>316.6523253223867</v>
       </c>
     </row>
     <row r="158">
@@ -7395,7 +7395,7 @@
         <v>156</v>
       </c>
       <c r="L158" t="n">
-        <v>314.1592653589793</v>
+        <v>316.6216341209777</v>
       </c>
     </row>
     <row r="159">
@@ -7439,7 +7439,7 @@
         <v>157</v>
       </c>
       <c r="L159" t="n">
-        <v>314.1592653589793</v>
+        <v>316.6271737189013</v>
       </c>
     </row>
     <row r="160">
@@ -7483,7 +7483,7 @@
         <v>158</v>
       </c>
       <c r="L160" t="n">
-        <v>314.1592653589793</v>
+        <v>316.6030225734833</v>
       </c>
     </row>
     <row r="161">
@@ -7527,7 +7527,7 @@
         <v>159</v>
       </c>
       <c r="L161" t="n">
-        <v>314.1592653589793</v>
+        <v>316.6025425699355</v>
       </c>
     </row>
     <row r="162">
@@ -7571,7 +7571,7 @@
         <v>160</v>
       </c>
       <c r="L162" t="n">
-        <v>314.1592653589793</v>
+        <v>316.5588351730509</v>
       </c>
     </row>
     <row r="163">
@@ -7615,7 +7615,7 @@
         <v>161</v>
       </c>
       <c r="L163" t="n">
-        <v>314.1592653589793</v>
+        <v>316.5324525438597</v>
       </c>
     </row>
     <row r="164">
@@ -7659,7 +7659,7 @@
         <v>162</v>
       </c>
       <c r="L164" t="n">
-        <v>314.1592653589793</v>
+        <v>316.6429017537891</v>
       </c>
     </row>
     <row r="165">
@@ -7703,7 +7703,7 @@
         <v>163</v>
       </c>
       <c r="L165" t="n">
-        <v>314.1592653589793</v>
+        <v>316.5472464894523</v>
       </c>
     </row>
     <row r="166">
@@ -7747,7 +7747,7 @@
         <v>164</v>
       </c>
       <c r="L166" t="n">
-        <v>314.1592653589793</v>
+        <v>316.5142305549545</v>
       </c>
     </row>
     <row r="167">
@@ -7791,7 +7791,7 @@
         <v>165</v>
       </c>
       <c r="L167" t="n">
-        <v>314.1592653589793</v>
+        <v>316.5033424213572</v>
       </c>
     </row>
     <row r="168">
@@ -7835,7 +7835,7 @@
         <v>166</v>
       </c>
       <c r="L168" t="n">
-        <v>314.1592653589793</v>
+        <v>316.5095522228258</v>
       </c>
     </row>
     <row r="169">
@@ -7879,7 +7879,7 @@
         <v>167</v>
       </c>
       <c r="L169" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4977360874286</v>
       </c>
     </row>
     <row r="170">
@@ -7923,7 +7923,7 @@
         <v>168</v>
       </c>
       <c r="L170" t="n">
-        <v>314.1592653589793</v>
+        <v>316.5198963992781</v>
       </c>
     </row>
     <row r="171">
@@ -7967,7 +7967,7 @@
         <v>169</v>
       </c>
       <c r="L171" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4949570043623</v>
       </c>
     </row>
     <row r="172">
@@ -8011,7 +8011,7 @@
         <v>170</v>
       </c>
       <c r="L172" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4949217930474</v>
       </c>
     </row>
     <row r="173">
@@ -8055,7 +8055,7 @@
         <v>171</v>
       </c>
       <c r="L173" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4938068880664</v>
       </c>
     </row>
     <row r="174">
@@ -8099,7 +8099,7 @@
         <v>172</v>
       </c>
       <c r="L174" t="n">
-        <v>314.1592653589793</v>
+        <v>324.3173917533691</v>
       </c>
     </row>
     <row r="175">
@@ -8143,7 +8143,7 @@
         <v>173</v>
       </c>
       <c r="L175" t="n">
-        <v>314.1592653589793</v>
+        <v>316.5212865265892</v>
       </c>
     </row>
     <row r="176">
@@ -8187,7 +8187,7 @@
         <v>174</v>
       </c>
       <c r="L176" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4933431236824</v>
       </c>
     </row>
     <row r="177">
@@ -8231,7 +8231,7 @@
         <v>175</v>
       </c>
       <c r="L177" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4956969465613</v>
       </c>
     </row>
     <row r="178">
@@ -8275,7 +8275,7 @@
         <v>176</v>
       </c>
       <c r="L178" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4973241165592</v>
       </c>
     </row>
     <row r="179">
@@ -8319,7 +8319,7 @@
         <v>177</v>
       </c>
       <c r="L179" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4931987137201</v>
       </c>
     </row>
     <row r="180">
@@ -8363,7 +8363,7 @@
         <v>178</v>
       </c>
       <c r="L180" t="n">
-        <v>314.1592653589793</v>
+        <v>316.5195376879311</v>
       </c>
     </row>
     <row r="181">
@@ -8407,7 +8407,7 @@
         <v>179</v>
       </c>
       <c r="L181" t="n">
-        <v>314.1592653589793</v>
+        <v>316.5195338428691</v>
       </c>
     </row>
     <row r="182">
@@ -8451,7 +8451,7 @@
         <v>180</v>
       </c>
       <c r="L182" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4933080905907</v>
       </c>
     </row>
     <row r="183">
@@ -8495,7 +8495,7 @@
         <v>181</v>
       </c>
       <c r="L183" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4938254204613</v>
       </c>
     </row>
     <row r="184">
@@ -8539,7 +8539,7 @@
         <v>182</v>
       </c>
       <c r="L184" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4951918035545</v>
       </c>
     </row>
   </sheetData>
